--- a/expense_reimburse_rpa/code/费用报销rpa配置表.xlsx
+++ b/expense_reimburse_rpa/code/费用报销rpa配置表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\xc\expense_reimburse_rpa\exe_file\dist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFA815C-EF7D-442C-AFA1-BC91371DFF90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31085DAF-07A4-4F20-9392-85E538B5FD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33495" yWindow="4575" windowWidth="17925" windowHeight="8850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33045" yWindow="5805" windowWidth="17925" windowHeight="8850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务商对应表" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>服务商名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -148,10 +148,6 @@
     <t>CGKJ-20250227-0006</t>
   </si>
   <si>
-    <t>北京神州光大科技有限公司1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>北京神州光大科技有限公司2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -245,6 +241,22 @@
   </si>
   <si>
     <t>D:\Google\ASP框架服务合同\2025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北华恒信通信技术有限公司</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>河北省</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>石家庄</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中国民生银行股份有限公司石家庄维明大街支行</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -588,6 +600,7 @@
   <cols>
     <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -633,19 +646,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="C3">
-        <v>123457</v>
+        <v>630996886</v>
       </c>
       <c r="D3" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="F3" t="s">
         <v>25</v>
@@ -653,7 +666,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -673,7 +686,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -758,15 +771,15 @@
         <v>10</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
@@ -788,81 +801,81 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2">
         <v>2001270</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/expense_reimburse_rpa/code/费用报销rpa配置表.xlsx
+++ b/expense_reimburse_rpa/code/费用报销rpa配置表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\xc\expense_reimburse_rpa\exe_file\dist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace\xc\expense_reimburse_rpa\code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31085DAF-07A4-4F20-9392-85E538B5FD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B2817-AD80-41F1-8C7E-68B036866CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33045" yWindow="5805" windowWidth="17925" windowHeight="8850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33045" yWindow="5805" windowWidth="17925" windowHeight="8850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="服务商对应表" sheetId="1" r:id="rId1"/>
@@ -782,7 +782,7 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
